--- a/TESTS/zlit_7_chornylne.xlsx
+++ b/TESTS/zlit_7_chornylne.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Корнелія Функе — німецька письменниця відома своїми фентезійними романами для підлітків</t>
+          <t>Корнелія Функе</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Фентезі — метафентезі де герої мають магічну здатність оживляти персонажів з книг читаючи вголос</t>
+          <t>Фентезі</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Деякі люди здатні «вичитувати» персонажів з книг в реальний світ — і водночас когось із реального відправляти у книгу</t>
+          <t>Деякі люди здатні «вичитувати» персонажів з книг в реальний світ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Мегіні (Мо) та його дочка Меґґі — обидва «срібноязикі»: коли Мо читає вголос персонажі оживають</t>
+          <t>Мегіні (Мо) та його дочка Меґґі</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -771,6 +796,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Лиходій Каппернік з книги що Мо колись вичитав — він вимагає прочитати йому певний персонаж</t>
+          <t>Лиходій Каппернік з книги що Мо колись вичитав</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -855,6 +890,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Хлопець вичитаний з «Тисячі і однієї ночі» разом з його Вогняним джином — живе у реальному світі</t>
+          <t>Хлопець вичитаний з «Тисячі і однієї ночі» разом з його Вогняним джином</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Страх і відповідальність — вона може вичитати маму але помилка може назавжди замурувати когось у книзі</t>
+          <t>Страх і відповідальність</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Хто така тітка Елінор і яка її пристрасть?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вчителька музики</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Самотня жінка, одержима колекціонуванням рідкісних і цінних книг</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Поліцейська</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Сусідка-ворог</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Чому Мо і Меґґі вирушили саме до тітки Елінор, рятуючись від небезпеки?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Випадково</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>У неї велика бібліотека, і вона могла надійно сховати їх та рідкісну книгу</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона жила далеко за кордоном</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона работорговець</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Як тітка Елінор ставилась до книг порівняно з людьми на початку роману?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Книги для неї нічого не означали</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Спершу книги цінувались нею навіть більше за стосунки з людьми, але це змінювалось</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона ненавиділа книги</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона продавала книги за гроші</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Хто такий Баста і кому він служить?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Друг Мо</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Жорстокий і марновірний підлеглий Каприкорна, що переслідує Мо й Меґґі</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Поліцейський</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Видавець</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Чого Баста особливо боявся, попри свою жорстокість?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого не боявся</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Марновірно боявся «поганих знаків», заклинань і чорних котів</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Боявся книг</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Боявся вогню</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>З якою метою Баста переслідував Мо аж до будинку тітки Елінор?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Щоб подружитися</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Щоб за наказом Каприкорна забрати Мо та рідкісну книгу «Чорнильне серце»</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Щоб попередити про небезпеку</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Випадково опинився там</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Де ховалось укриття Каприкорна та його людей?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>У великому місті</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>У занедбаному гірському італійському селі, яке він захопив і перетворив на свою базу</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>У підземеллі</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>На кораблі</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Чим займались люди Каприкорна в селі?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Землеробством</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Грабунками, підпалами та залякуванням навколишніх поселень</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Туризмом</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нічим, жили мирно</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Що Каприкорн хотів отримати від Мо, утримуючи його в селі?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Гроші</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Щоб Мо своїм голосом «вичитав» йому з книг скарби та небезпечну істоту Тінь</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Звільнення</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нову книгу</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Хто такий Феноліо і яке його значення для сюжету?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Випадковий старий</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Сам автор книги «Чорнильне серце», якого знайшли живим у тому ж селі</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Лікар</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Поліцейський слідчий</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Як Феноліо почувався, дізнавшись, що його персонажі справді існують у реальному світі?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Йому було байдуже</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Здивованим і водночас зацікавленим — і він погодився допомогти, дописавши новий текст</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він злякався і втік</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він не повірив нікому</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Яку допомогу Феноліо міг надати Мо і Меґґі завдяки своєму авторству?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Жодної</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Написати нові слова, які за допомогою «срібноязикості» можна було б «вичитати» в реальність</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Дати їм гроші</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Викликати поліцію</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Хто такий Прахвіст і звідки він з'явився у реальному світі?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Звичайна людина</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Майстер вогню, персонаж, якого Мо багато років тому «вичитав» із книги «Чорнильне серце»</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Поліцейський</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Сусід Меґґі</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Чого найбільше прагнув Прахвіст протягом усього роману?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Залишитись у реальному світі назавжди</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Повернутися назад у світ книги «Чорнильне серце», звідки він прийшов</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Стати багатим</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Знайти нову роботу</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Як прагнення Прахвіста повернутись у книгу впливало на його ставлення до Мо і Меґґі?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він завжди був вірним другом</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він діяв неоднозначно — допомагав, але іноді зраджував їх, якщо це наближало його до повернення додому</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він був їхнім ворогом весь час</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він не звертав на них уваги</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Який план вигадали Феноліо, Мо і Меґґі, щоб позбутися Каприкорна?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Втекти всі разом</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Написати і «вичитати» в реальність Тінь — небезпечну істоту з книги, яка має знищити Каприкорна</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Викликати поліцію</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Підпалити село</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Хто з героїв виявляється також володіє «срібним голосом», як і Мо?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Лише Мо</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Виявляється, що й Меґґі має той самий дар «срібноязикості», як і батько</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Ніхто більше</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Тітка Елінор</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Що сталося з Каприкорном, коли план з Тінню здійснився?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він утік</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Тінь, підкоряючись новому тексту, знищила Каприкорна</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Каприкорн переміг Тінь</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нічого не сталося</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Хто така Реза, яка з'являється у фінальній частині роману?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нова подруга Меґґі</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Дружина Мо і мати Меґґі, яка багато років тому опинилась усередині книги «Чорнильне серце»</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Ворог Мо</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Сестра Елінор</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Як Резу вдалось повернути у реальний світ?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вона сама вийшла</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Завдяки силі «срібноязикості» Мо та Меґґі, які «вичитали» її назад зі сторінок книги</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Каприкорн її відпустив</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона залишилась у книзі назавжди</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Якою стає родина Мо, Рези і Меґґі наприкінці роману?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вони розлучаються назавжди</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вони нарешті знову разом — родина, розділена багато років через магію слова, відновлюється</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вони залишаються в книзі</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Ніхто не виживає</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Що таке «метафентезі» і як «Чорнильне серце» відповідає цьому визначенню?</t>
+          <t>«Метафентезі» — це фентезі про самі книги, історії та письменство; «Чорнильне серце» є прикладом такого твору.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Яку роль відіграє «Тисяча і одна ніч» у романі?</t>
+          <t>«Тисяча і одна ніч» у романі — джерело, з якого «вичитали» персонажа Фаріда та його вогняного джина.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,29 +2170,32 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Що спільного між «Чорнильним серцем» Функе і «Мандрівним замком Хаула» Джонс для 7 класу?</t>
+          <t>«Чорнильне серце» Функе і «Мандрівний замок Хаула» Джонс не мають жодних спільних рис як фентезійні романи.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея «Чорнильного серця»?</t>
+          <t>Головна ідея «Чорнильного серця» — слово і книга мають справжню силу, тож читання й писання — це відповідальність, а не лише розвага.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Яку роль відіграє Прахвост і яке його значення?</t>
+          <t>Прахвіст у романі прагне повернутися у вигаданий світ книги, звідки він прийшов.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Що «Чорнильне серце» говорить про стосунки читача і книги?</t>
+          <t>«Чорнильне серце» стверджує, що книги і реальність абсолютно не пов'язані між собою і ніяк не впливають одна на одну.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які теми розкриває «Чорнильне серце»?</t>
+          <t>Що відбувається у романі «Чорнильне серце»?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Сила слова і відповідальність за нього</t>
+          <t>Прахвіст хоче повернутись у книгу</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Межа між реальним і вигаданим</t>
+          <t>Феноліо допомагає новим текстом</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Небезпека читання вголос</t>
+          <t>Каприкорн перемагає назавжди</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Любов батька і дочки</t>
+          <t>Резу повертають у реальний світ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Книги — магічні портали і джерела життя; читання — акт творення і відповідальності</t>
+          <t>Книги</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Слово має фізичну силу — вимовлене слово (читання) створює і знищує реальності; мова є найпотужнішою магією</t>
+          <t>Слово має фізичну силу</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Творчу силу митця — здатність творів мистецтва (книг) оживати і впливати на реальність</t>
+          <t>Творчу силу митця</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
